--- a/public/system/export/asset.xlsx
+++ b/public/system/export/asset.xlsx
@@ -1,12 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="570" windowWidth="24615" windowHeight="11955"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="4. Mẫu Nhập Tài Sản" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="lDT5JqXZt4NKODR45x6Wo13oR1bg0vRusL1x2CP3qp8="/>
@@ -16,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>STT</t>
   </si>
@@ -24,15 +27,6 @@
     <t>Tên Thiết Bị</t>
   </si>
   <si>
-    <t>Nước sản xuất</t>
-  </si>
-  <si>
-    <t>Năm sản xuất</t>
-  </si>
-  <si>
-    <t>Số  lượng</t>
-  </si>
-  <si>
     <t>Đơn Vị</t>
   </si>
   <si>
@@ -48,91 +42,108 @@
     <t>Bộ môn</t>
   </si>
   <si>
-    <t>Phân Loại</t>
-  </si>
-  <si>
-    <t>Ống nghiệm Φ12</t>
+    <t>SỞ GD&amp;ĐT ...</t>
+  </si>
+  <si>
+    <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
+  </si>
+  <si>
+    <t>TRƯỜNG …</t>
+  </si>
+  <si>
+    <t>Độc lập - Tự do - Hạnh phúc</t>
+  </si>
+  <si>
+    <t>Bàn thực hành</t>
   </si>
   <si>
     <t>Cái</t>
   </si>
   <si>
-    <t>Phòng Tiếng Anh</t>
-  </si>
-  <si>
-    <t>Vật Lý-Trải nghiệm</t>
-  </si>
-  <si>
-    <t>Tài sản</t>
-  </si>
-  <si>
-    <t>Ống nghiệm Φ16</t>
-  </si>
-  <si>
-    <t>Hỏng 15</t>
-  </si>
-  <si>
-    <t>Ống nghiệm Φ20</t>
-  </si>
-  <si>
-    <t>cái</t>
-  </si>
-  <si>
-    <t>Hỏng 35</t>
-  </si>
-  <si>
-    <t>Ống nghiệm Φ16 có nhánh</t>
-  </si>
-  <si>
-    <t>Ống nghiệm Φ24 có nhánh</t>
-  </si>
-  <si>
-    <t>Ống nghiệm 2 nhánh chữ Y</t>
-  </si>
-  <si>
-    <t>Ống hút nhỏ giọt</t>
-  </si>
-  <si>
-    <t>Hỏng 06</t>
-  </si>
-  <si>
-    <t>Ống đong hình trụ 100ml</t>
-  </si>
-  <si>
-    <t>Hỏng 08</t>
-  </si>
-  <si>
-    <t>Ống hình trụ rỗng 2 đầu</t>
-  </si>
-  <si>
-    <t>Ống thuỷ tinh hình trụ loe 1 đầu</t>
+    <t>Thiết bị môn Công nghệ - NN</t>
+  </si>
+  <si>
+    <t>Công nghệ -CN và NN</t>
+  </si>
+  <si>
+    <t>Hỏng 02</t>
+  </si>
+  <si>
+    <t>Ngày xuất:</t>
+  </si>
+  <si>
+    <t>Năm SX</t>
+  </si>
+  <si>
+    <t>Số lượng</t>
+  </si>
+  <si>
+    <t>DANH SÁCH TÀI SẢN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="9">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -140,36 +151,115 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -359,379 +449,292 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:I1008"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.63"/>
-    <col customWidth="1" min="2" max="2" width="34.25"/>
-    <col customWidth="1" min="3" max="6" width="12.63"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="15" customHeight="1">
+      <c r="A1" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+    </row>
+    <row r="2" spans="1:9" ht="15" customHeight="1">
+      <c r="A2" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="25.5" customHeight="1">
+      <c r="A4" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="15" customHeight="1">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="19"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A9" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F9" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A10" s="12">
+        <v>1</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="14">
+        <v>2021</v>
+      </c>
+      <c r="D10" s="14">
+        <v>10</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="14">
+        <v>250</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A11" s="11">
+        <v>2</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A12" s="11">
+        <v>3</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A13" s="11">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A14" s="11">
+        <v>5</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A15" s="11">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A19" s="11">
         <v>10</v>
       </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="3">
-        <v>2007.0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>50.0</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2007.0</v>
-      </c>
-      <c r="E3" s="3">
-        <v>35.0</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2007.0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>65.0</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2007.0</v>
-      </c>
-      <c r="E5" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1.61</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2007.0</v>
-      </c>
-      <c r="E6" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="3">
-        <v>2007.0</v>
-      </c>
-      <c r="E7" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="3">
-        <v>2007.0</v>
-      </c>
-      <c r="E8" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3">
-        <v>2007.0</v>
-      </c>
-      <c r="E9" s="3">
-        <v>18.0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="3">
-        <v>2007.0</v>
-      </c>
-      <c r="E10" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2.54</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="3">
-        <v>2007.0</v>
-      </c>
-      <c r="E11" s="3">
-        <v>26.0</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="20" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -1700,7 +1703,23 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="E2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>